--- a/output/Tables/Description/Drivers/short_drivers_proportion.xlsx
+++ b/output/Tables/Description/Drivers/short_drivers_proportion.xlsx
@@ -373,13 +373,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>30.41823654026132</v>
+        <v>33.65873121947073</v>
       </c>
       <c r="B2">
-        <v>29.25609228370711</v>
+        <v>32.47619554420612</v>
       </c>
       <c r="C2">
-        <v>31.58038079681553</v>
+        <v>34.84126689473535</v>
       </c>
     </row>
   </sheetData>
